--- a/Instructions and Theory/9. Statement and Data Notes.xlsx
+++ b/Instructions and Theory/9. Statement and Data Notes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/Instructions and Theory/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1997F8-5DE7-D749-B9A5-FE222ECC9342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937F42B2-24C1-1E43-8DC9-9887196DF794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="100" windowWidth="25440" windowHeight="13540" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Debt is formed from finance and operating leases</t>
   </si>
@@ -113,6 +113,12 @@
   </si>
   <si>
     <t>A proxy for cost of debt is to find the closest bonds with maturity 10 years from now and get the yield to maturity</t>
+  </si>
+  <si>
+    <t>Continuing/Discontinued operations</t>
+  </si>
+  <si>
+    <t>Always use net income from continuing operations in the income statement under Net income and for all ratios</t>
   </si>
 </sst>
 </file>
@@ -570,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="A2:G24"/>
+  <dimension ref="A2:G28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -686,11 +692,28 @@
         <v>22</v>
       </c>
     </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B28" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A26:G26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
